--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC915C6-97F4-4F11-926C-B4ECC263D6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC7D38D-8E22-49FE-AF3C-1F00ACFEA1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -360,6 +360,35 @@
   </si>
   <si>
     <t>ステージ選択画面のBackでも値の初期化を実行する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>位置を少し左に移動させて再エクスポート</t>
+    <rPh sb="0" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ボタンの位置を調整</t>
+    <rPh sb="4" eb="6">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チョウセイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -802,26 +831,45 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4"/>
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>

--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC7D38D-8E22-49FE-AF3C-1F00ACFEA1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F6B9B-38D3-47CB-BDA1-D188A0348369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -388,6 +388,73 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ダメージを受けたときに画面を赤く明滅させるようにした</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ダメージを受けた時、一定時間移動速度を0にして一時的に移動できなくした</t>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>文字を修正した</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヒットストップ中にもう一度ダメージを受けたら半分のダメージを与えるように設定</t>
+    <rPh sb="7" eb="8">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -826,6 +893,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4"/>
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1106,9 +1174,15 @@
       </c>
     </row>
     <row r="49" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B49" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="C49" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="50" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
@@ -1117,13 +1191,23 @@
       <c r="B50" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="C50" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="51" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="B51" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="C51" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
       </c>
@@ -1134,6 +1218,9 @@
       </c>
       <c r="B54" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">

--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F6B9B-38D3-47CB-BDA1-D188A0348369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089F0E20-44B0-492B-896F-7B99D65CE8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -109,12 +109,6 @@
   </si>
   <si>
     <t>　ここも画面上部などにSTAGE SELECTなど表示したほうが良い</t>
-  </si>
-  <si>
-    <t>　ボタン周りの挙動がおかしく感じる、武器選択と同じようにStartボタンを用意してほしい</t>
-  </si>
-  <si>
-    <t>　　＜＞のボタンで選択して、右下Startなどで開始したほうがわかりやすい</t>
   </si>
   <si>
     <t>　クリアしてこの画面に戻ってくるとBGMが消えている</t>
@@ -456,6 +450,10 @@
     <rPh sb="36" eb="38">
       <t>セッテイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　ボタン周りの挙動がおかしく感じる、＜＞のボタンで選択して、右下Startなどで開始したほうがわかりやすい</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -883,13 +881,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -900,7 +898,7 @@
     </row>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
@@ -908,24 +906,24 @@
     </row>
     <row r="5" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -936,7 +934,7 @@
     </row>
     <row r="9" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
@@ -950,18 +948,18 @@
     </row>
     <row r="12" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -969,7 +967,7 @@
     </row>
     <row r="14" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -977,7 +975,7 @@
     </row>
     <row r="15" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
@@ -985,7 +983,7 @@
     </row>
     <row r="16" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
@@ -993,13 +991,13 @@
     </row>
     <row r="17" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1010,24 +1008,24 @@
     </row>
     <row r="20" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1037,7 +1035,7 @@
     </row>
     <row r="24" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>17</v>
@@ -1045,18 +1043,18 @@
     </row>
     <row r="25" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
@@ -1064,7 +1062,7 @@
     </row>
     <row r="27" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -1072,7 +1070,7 @@
     </row>
     <row r="28" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>21</v>
@@ -1090,7 +1088,7 @@
     </row>
     <row r="32" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>24</v>
@@ -1098,129 +1096,124 @@
     </row>
     <row r="33" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
       <c r="B42" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="4"/>
       <c r="B53" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1229,40 +1222,40 @@
     <row r="57" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57"/>
       <c r="B57" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="C58" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089F0E20-44B0-492B-896F-7B99D65CE8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB66B0A-2DD9-49A6-8019-6DB4BDDF1ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>　Startボタンは枠外右下へ、Backの対面に来るような位置へ</t>
-  </si>
-  <si>
-    <t>　装備の説明は武器アイコンと動画の間に入れる、今だと視線移動が多くしんどい</t>
   </si>
   <si>
     <t>ステージ選択画面</t>
@@ -454,6 +451,10 @@
   </si>
   <si>
     <t>　ボタン周りの挙動がおかしく感じる、＜＞のボタンで選択して、右下Startなどで開始したほうがわかりやすい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>　装備の説明は武器アイコンと動画の間に入れる、今だと視線移動が多くしんどい</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -881,13 +882,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -898,7 +899,7 @@
     </row>
     <row r="4" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>1</v>
@@ -906,24 +907,24 @@
     </row>
     <row r="5" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -934,7 +935,7 @@
     </row>
     <row r="9" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
@@ -948,18 +949,18 @@
     </row>
     <row r="12" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>8</v>
@@ -967,7 +968,7 @@
     </row>
     <row r="14" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
@@ -975,7 +976,7 @@
     </row>
     <row r="15" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
@@ -983,7 +984,7 @@
     </row>
     <row r="16" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
@@ -991,13 +992,13 @@
     </row>
     <row r="17" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1008,24 +1009,24 @@
     </row>
     <row r="20" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1035,7 +1036,7 @@
     </row>
     <row r="24" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>17</v>
@@ -1043,18 +1044,18 @@
     </row>
     <row r="25" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
@@ -1062,7 +1063,7 @@
     </row>
     <row r="27" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>20</v>
@@ -1070,7 +1071,7 @@
     </row>
     <row r="28" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>21</v>
@@ -1078,142 +1079,147 @@
     </row>
     <row r="29" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="3" t="s">
+    <row r="38" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
       <c r="B42" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4"/>
       <c r="B48" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="4"/>
       <c r="B53" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1222,40 +1228,40 @@
     <row r="57" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57"/>
       <c r="B57" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB66B0A-2DD9-49A6-8019-6DB4BDDF1ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F473316-6C40-47FE-AB68-260EABA7CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -455,6 +455,16 @@
   </si>
   <si>
     <t>　装備の説明は武器アイコンと動画の間に入れる、今だと視線移動が多くしんどい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ステージ選択のスクリプトを見直し、Startでゲームスタートできるようにした</t>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ミナオ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1095,12 +1105,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
         <v>39</v>
       </c>
@@ -1108,13 +1124,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="4"/>
       <c r="B37" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
@@ -1122,7 +1138,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
@@ -1130,7 +1146,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
@@ -1138,13 +1154,13 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="4"/>
       <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
         <v>39</v>
       </c>
@@ -1152,13 +1168,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4"/>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
         <v>39</v>
       </c>
@@ -1166,7 +1182,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="4"/>
       <c r="B48" s="3" t="s">
         <v>32</v>

--- a/チーム制作　改善点.xlsx
+++ b/チーム制作　改善点.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\Team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F473316-6C40-47FE-AB68-260EABA7CA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBD2C10-969E-49E0-B0D2-73C57F05D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7EDA004-E390-4B83-9276-E0FDCD60E4A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
   <si>
     <t>タイトル画面</t>
   </si>
@@ -464,6 +464,54 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>動画の位置を上に移動させその下に武器の説明テキストを移動させた</t>
+    <rPh sb="0" eb="2">
+      <t>ドウガ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ブキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラスボスが出現しない</t>
+    <rPh sb="5" eb="7">
+      <t>シュツゲン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラスボスの出現フラグが機能するように設定</t>
+    <rPh sb="5" eb="7">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -882,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE868454-41E9-41A7-BD24-01183C0D4D7B}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultColWidth="19.875" defaultRowHeight="33" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.875" style="2"/>
@@ -1088,8 +1136,14 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -1278,6 +1332,17 @@
       </c>
       <c r="C60" s="1" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
